--- a/Manuel Validation/CAS S03/Cas S03.xlsx
+++ b/Manuel Validation/CAS S03/Cas S03.xlsx
@@ -537,7 +537,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -818,7 +818,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -972,7 +972,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -984,7 +984,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1001,6 +1001,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2111,7 +2114,7 @@
         <v>95</v>
       </c>
       <c r="U40" s="62">
-        <f t="shared" ref="U40:U43" si="0">S40*T40/1000</f>
+        <f t="shared" ref="U40:U42" si="0">S40*T40/1000</f>
         <v>29.782499999999999</v>
       </c>
     </row>
@@ -2185,7 +2188,7 @@
       <c r="P43" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="Q43" s="64">
+      <c r="Q43" s="80">
         <f>(Nfs*ABS(zANP-tfs/2)+Nfi*ABS(zANP-(Ht-tfi/2))+Nw*hw/2*(pW^2+(1-pW)^2))/1000</f>
         <v>275.88</v>
       </c>
@@ -2512,8 +2515,8 @@
         <v>135</v>
       </c>
       <c r="N69" s="61">
-        <f>-qQ_1*La^2*LL/18/SQRT(3)/(E*InertieCM4/100)*1000^2</f>
-        <v>-4.4387477937325341</v>
+        <f>-qQ_1*La^2*LL^2/18/SQRT(3)/(E*InertieCM4/100)*1000^2</f>
+        <v>-39.948730143592805</v>
       </c>
       <c r="O69" t="s">
         <v>7</v>
@@ -2670,7 +2673,7 @@
         <v>124</v>
       </c>
       <c r="E90" s="5">
-        <v>4189</v>
+        <v>279</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
@@ -2682,7 +2685,7 @@
       </c>
       <c r="E91" s="59">
         <f>SQRT(MRd*GammaM0/Mcr)</f>
-        <v>0.25662852539759506</v>
+        <v>0.99439288226589551</v>
       </c>
     </row>
     <row r="92" spans="3:6" x14ac:dyDescent="0.25">
@@ -2699,7 +2702,7 @@
       </c>
       <c r="E93" s="60">
         <f>0.5*(1+AlphaLT*(LambdaLT-0.2)+LambdaLT^2)</f>
-        <v>0.5544479396749582</v>
+        <v>1.2962778974115778</v>
       </c>
     </row>
     <row r="94" spans="3:6" x14ac:dyDescent="0.25">
@@ -2708,7 +2711,7 @@
       </c>
       <c r="E94" s="69">
         <f>1/(PhiLT+SQRT(PhiLT^2-LambdaLT^2))</f>
-        <v>0.95608720441625272</v>
+        <v>0.46995700637303306</v>
       </c>
     </row>
     <row r="95" spans="3:6" x14ac:dyDescent="0.25">
@@ -2717,7 +2720,7 @@
       </c>
       <c r="E95" s="62">
         <f>KhiLT*MRd*GammaM0/GammaM1</f>
-        <v>263.7653379543558</v>
+        <v>129.65173891819236</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
@@ -2733,7 +2736,7 @@
       </c>
       <c r="E97" s="75">
         <f>MEd_U1/E95</f>
-        <v>-0.88857391883901837</v>
+        <v>-1.8077273930578432</v>
       </c>
     </row>
     <row r="98" spans="4:5" x14ac:dyDescent="0.25">

--- a/Manuel Validation/CAS S03/Cas S03.xlsx
+++ b/Manuel Validation/CAS S03/Cas S03.xlsx
@@ -43,6 +43,8 @@
     <definedName name="Ht">Feuil1!$D$12</definedName>
     <definedName name="hw">Feuil1!$D$8</definedName>
     <definedName name="InertieCM4">Feuil1!$N$26</definedName>
+    <definedName name="Izfi">Feuil1!$V$18</definedName>
+    <definedName name="Izfs">Feuil1!$V$17</definedName>
     <definedName name="KhiLT">Feuil1!$E$94</definedName>
     <definedName name="KhiW">Feuil1!$E$70</definedName>
     <definedName name="kTau">Feuil1!$E$68</definedName>
@@ -95,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="156">
   <si>
     <t xml:space="preserve">PRS </t>
   </si>
@@ -527,6 +529,42 @@
   </si>
   <si>
     <t>Nidi</t>
+  </si>
+  <si>
+    <t>Inertie de torsion</t>
+  </si>
+  <si>
+    <t>Itfs</t>
+  </si>
+  <si>
+    <t>Itfi</t>
+  </si>
+  <si>
+    <t>Iw</t>
+  </si>
+  <si>
+    <t>Itns</t>
+  </si>
+  <si>
+    <t>Itni</t>
+  </si>
+  <si>
+    <t>It</t>
+  </si>
+  <si>
+    <t>Inertie de gauchissement</t>
+  </si>
+  <si>
+    <t>Izfs</t>
+  </si>
+  <si>
+    <t>Izfi</t>
+  </si>
+  <si>
+    <t>mm6</t>
+  </si>
+  <si>
+    <t>cm6</t>
   </si>
 </sst>
 </file>
@@ -539,7 +577,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,8 +609,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -666,6 +712,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -818,7 +870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1006,6 +1058,7 @@
     <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1291,13 +1344,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C4:V99"/>
+  <dimension ref="C4:X99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1316,8 +1370,14 @@
       <c r="N4" s="7"/>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
-    </row>
-    <row r="6" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S4" s="81" t="s">
+        <v>144</v>
+      </c>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81"/>
+    </row>
+    <row r="6" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>1</v>
       </c>
@@ -1342,8 +1402,18 @@
       <c r="N6" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S6" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="T6" s="63">
+        <f>bfs*tfs^3/3*(1-0.63*tfs/bfs*(1-tfs^4/12/bfs^4))</f>
+        <v>269555.42093690881</v>
+      </c>
+      <c r="U6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
@@ -1368,8 +1438,18 @@
       <c r="N7" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S7" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="T7" s="63">
+        <f>bfi*tfi^3/3*(1-0.63*tfi/bfi*(1-tfi^4/12/bfi^4))</f>
+        <v>483208.13694377651</v>
+      </c>
+      <c r="U7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C8" s="3" t="s">
         <v>3</v>
       </c>
@@ -1394,8 +1474,18 @@
       <c r="N8" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S8" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="T8" s="5">
+        <f>1/3*hw*tw^3</f>
+        <v>20160</v>
+      </c>
+      <c r="U8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C9" s="3" t="s">
         <v>4</v>
       </c>
@@ -1411,8 +1501,18 @@
       <c r="N9" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S9" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="T9" s="63">
+        <f>0.15*tw/tfs*((tfs^2+tw^2/4)/tfs)^4</f>
+        <v>5856.7531249999993</v>
+      </c>
+      <c r="U9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1428,8 +1528,18 @@
       <c r="N10" s="6">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="11" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S10" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="T10" s="63">
+        <f>0.15*tw/tfi*((tfi^2+tw^2/4)/tfi)^4</f>
+        <v>10316.12943277673</v>
+      </c>
+      <c r="U10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
@@ -1445,8 +1555,18 @@
       <c r="N11" s="6">
         <v>1.25</v>
       </c>
-    </row>
-    <row r="12" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="S11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="T11" s="63">
+        <f>SUM(T6:T10)</f>
+        <v>789096.44043846207</v>
+      </c>
+      <c r="U11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
@@ -1464,7 +1584,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C13" s="3"/>
       <c r="H13" s="10" t="s">
         <v>9</v>
@@ -1480,7 +1600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
@@ -1502,7 +1622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C15" s="50" t="s">
         <v>47</v>
       </c>
@@ -1534,8 +1654,14 @@
       <c r="Q15" s="52"/>
       <c r="R15" s="52"/>
       <c r="S15" s="52"/>
-    </row>
-    <row r="16" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U15" s="81" t="s">
+        <v>151</v>
+      </c>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="81"/>
+    </row>
+    <row r="16" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C16" s="50" t="s">
         <v>48</v>
       </c>
@@ -1558,7 +1684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:23" x14ac:dyDescent="0.25">
       <c r="H17" s="22" t="s">
         <v>11</v>
       </c>
@@ -1590,8 +1716,15 @@
       <c r="S17" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U17" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="V17" s="5">
+        <f>1/12*bfs^3*tfs</f>
+        <v>5062500</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C18" s="50" t="s">
         <v>102</v>
       </c>
@@ -1639,8 +1772,15 @@
         <f>bfs*tfs^3/12</f>
         <v>72900</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U18" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="V18" s="5">
+        <f>1/12*bfi^3*tfi</f>
+        <v>6187500</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.25">
       <c r="M19" s="41" t="s">
         <v>32</v>
       </c>
@@ -1668,8 +1808,18 @@
         <f>hw^3*tw/12</f>
         <v>10976000</v>
       </c>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="V19" s="5">
+        <f>Izfs*Izfi/(Izfs+Izfi)*(Ht-tfs/2-tfi/2)^2</f>
+        <v>250593750000</v>
+      </c>
+      <c r="W19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>24</v>
       </c>
@@ -1703,8 +1853,16 @@
         <f>bfi*tfi^3/12</f>
         <v>133100</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U20" s="2"/>
+      <c r="V20" s="63">
+        <f>V19/10^6</f>
+        <v>250593.75</v>
+      </c>
+      <c r="W20" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C21" s="3"/>
       <c r="H21" s="1" t="s">
         <v>27</v>
@@ -1728,8 +1886,10 @@
         <f>SUM(S18:S20)</f>
         <v>11182000</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U21" s="2"/>
+      <c r="V21" s="4"/>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C22" s="3" t="s">
         <v>25</v>
       </c>
@@ -1739,8 +1899,10 @@
       <c r="E22" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U22" s="2"/>
+      <c r="V22" s="4"/>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C23" s="3" t="s">
         <v>131</v>
       </c>
@@ -1773,8 +1935,10 @@
       <c r="O23" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U23" s="2"/>
+      <c r="V23" s="4"/>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.25">
       <c r="H24" s="32"/>
       <c r="I24" s="33" t="s">
         <v>16</v>
@@ -1796,8 +1960,10 @@
       <c r="O24" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
+      <c r="U24" s="2"/>
+      <c r="V24" s="4"/>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C25" s="3" t="s">
         <v>120</v>
       </c>
@@ -1841,7 +2007,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C26" s="3"/>
       <c r="D26" s="4"/>
       <c r="H26" s="38"/>
@@ -1873,7 +2039,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C27" s="3"/>
       <c r="D27" s="4"/>
       <c r="P27" s="3" t="s">
@@ -1887,11 +2053,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C28" s="3"/>
       <c r="D28" s="4"/>
     </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C29" s="3"/>
       <c r="D29" s="4"/>
       <c r="M29" s="52" t="s">
@@ -1904,7 +2070,7 @@
       <c r="R29" s="52"/>
       <c r="S29" s="52"/>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C30" s="3"/>
       <c r="D30" s="4"/>
       <c r="I30" s="3" t="s">
@@ -1918,7 +2084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C31" s="3"/>
       <c r="D31" s="4"/>
       <c r="I31" s="3" t="s">
@@ -1942,7 +2108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C32" s="65" t="s">
         <v>64</v>
       </c>

--- a/Manuel Validation/CAS S03/Cas S03.xlsx
+++ b/Manuel Validation/CAS S03/Cas S03.xlsx
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="157">
   <si>
     <t xml:space="preserve">PRS </t>
   </si>
@@ -565,6 +565,9 @@
   </si>
   <si>
     <t>cm6</t>
+  </si>
+  <si>
+    <t>Sem inf</t>
   </si>
 </sst>
 </file>
@@ -1729,7 +1732,7 @@
         <v>102</v>
       </c>
       <c r="D18" s="6">
-        <v>470</v>
+        <v>370</v>
       </c>
       <c r="E18" t="s">
         <v>49</v>
@@ -2767,13 +2770,23 @@
       <c r="F79" t="s">
         <v>83</v>
       </c>
+      <c r="H79" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I79" s="61">
+        <f>(bfi*tfi*(Ht-ABS(zG)-tfi/2))/1000</f>
+        <v>457.05</v>
+      </c>
+      <c r="J79" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="80" spans="3:18" x14ac:dyDescent="0.25">
       <c r="C80" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D81" s="2" t="s">
         <v>100</v>
       </c>
@@ -2784,8 +2797,18 @@
       <c r="F81" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="H81" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I81" s="62">
+        <f>VEd_U1*(I79/InertieCM4)*100</f>
+        <v>590.32896368345632</v>
+      </c>
+      <c r="J81" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D82" s="2" t="s">
         <v>101</v>
       </c>
@@ -2796,65 +2819,109 @@
       <c r="F82" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="H82" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I82" s="62">
+        <f>VEd_U2*(I79/InertieCM4)*100</f>
+        <v>413.23027457841943</v>
+      </c>
+      <c r="J82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D83" s="2" t="s">
         <v>105</v>
       </c>
       <c r="E83" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
+        <v>0.85</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I83" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="L83" s="4"/>
+      <c r="M83" s="4"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="L84" s="4"/>
+      <c r="M84" s="4"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D85" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E85" s="60">
         <f>E81/Fu*GammaM2*SQRT(3)/2*BetaW</f>
-        <v>1.1674867639193185</v>
+        <v>1.4006335200773805</v>
       </c>
       <c r="F85" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="H85" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I85" s="60">
+        <f>I81/Fu*GammaM2*SQRT(3)/2*BetaW</f>
+        <v>1.4680874907725416</v>
+      </c>
+      <c r="J85" t="s">
+        <v>7</v>
+      </c>
+      <c r="L85" s="4"/>
+      <c r="M85" s="4"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D86" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E86" s="60">
         <f>E82/Fu*GammaM2*SQRT(3)/2*BetaW</f>
-        <v>0.81724073474352288</v>
+        <v>0.98044346405416638</v>
       </c>
       <c r="F86" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="H86" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I86" s="60">
+        <f>I82/Fu*GammaM2*SQRT(3)/2*BetaW</f>
+        <v>1.0276612435407788</v>
+      </c>
+      <c r="J86" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C89" s="67" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D90" s="2" t="s">
         <v>124</v>
       </c>
       <c r="E90" s="5">
-        <v>279</v>
+        <v>632</v>
       </c>
       <c r="F90" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D91" s="3" t="s">
         <v>125</v>
       </c>
       <c r="E91" s="59">
         <f>SQRT(MRd*GammaM0/Mcr)</f>
-        <v>0.99439288226589551</v>
-      </c>
-    </row>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
+        <v>0.66069583572304447</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D92" s="3" t="s">
         <v>127</v>
       </c>
@@ -2862,37 +2929,37 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D93" s="3" t="s">
         <v>126</v>
       </c>
       <c r="E93" s="60">
         <f>0.5*(1+AlphaLT*(LambdaLT-0.2)+LambdaLT^2)</f>
-        <v>1.2962778974115778</v>
-      </c>
-    </row>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
+        <v>0.89332391124564292</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D94" s="3" t="s">
         <v>128</v>
       </c>
       <c r="E94" s="69">
         <f>1/(PhiLT+SQRT(PhiLT^2-LambdaLT^2))</f>
-        <v>0.46995700637303306</v>
-      </c>
-    </row>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
+        <v>0.66908438848015528</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D95" s="3" t="s">
         <v>129</v>
       </c>
       <c r="E95" s="62">
         <f>KhiLT*MRd*GammaM0/GammaM1</f>
-        <v>129.65173891819236</v>
+        <v>184.58700109390523</v>
       </c>
       <c r="F95" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D96" s="3"/>
       <c r="E96" s="4"/>
     </row>
@@ -2901,8 +2968,8 @@
         <v>130</v>
       </c>
       <c r="E97" s="75">
-        <f>MEd_U1/E95</f>
-        <v>-1.8077273930578432</v>
+        <f>ABS(MEd_U1/E95)</f>
+        <v>1.2697264629201384</v>
       </c>
     </row>
     <row r="98" spans="4:5" x14ac:dyDescent="0.25">
